--- a/reports/pdf_change_20260721.xlsx
+++ b/reports/pdf_change_20260721.xlsx
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -567,14 +567,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>캡처 4/7  ·  대기: TIME, TIME, TIGER</t>
+          <t>캡처 6/7  ·  대기: TIGER</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,592억   ·   현금 85억(2.0%)      당일 2026-07-21  vs  전영업일 2026-07-20      매수 1종목  /  매도 3종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,237억   ·   현금 85억(2.0%)      당일 2026-07-21  vs  전영업일 2026-07-20      매수 1종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -763,7 +763,7 @@
     <row r="10" ht="19" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,085억   ·   현금 11억(0.3%)      당일 2026-07-21  vs  전영업일 2026-07-20      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,823억   ·   현금 11억(0.3%)      당일 2026-07-21  vs  전영업일 2026-07-20      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B10" s="4" t="n"/>
@@ -785,274 +785,622 @@
       </c>
     </row>
     <row r="13" ht="19" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B13" s="20" t="n"/>
-      <c r="C13" s="20" t="n"/>
-      <c r="D13" s="20" t="n"/>
-      <c r="E13" s="20" t="n"/>
-      <c r="F13" s="20" t="n"/>
-      <c r="G13" s="20" t="n"/>
-      <c r="H13" s="20" t="n"/>
-      <c r="I13" s="20" t="n"/>
-      <c r="J13" s="20" t="n"/>
-      <c r="K13" s="20" t="n"/>
-    </row>
-    <row r="15" ht="19" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B15" s="20" t="n"/>
-      <c r="C15" s="20" t="n"/>
-      <c r="D15" s="20" t="n"/>
-      <c r="E15" s="20" t="n"/>
-      <c r="F15" s="20" t="n"/>
-      <c r="G15" s="20" t="n"/>
-      <c r="H15" s="20" t="n"/>
-      <c r="I15" s="20" t="n"/>
-      <c r="J15" s="20" t="n"/>
-      <c r="K15" s="20" t="n"/>
-    </row>
-    <row r="17" ht="19" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 341억   ·   현금 2억(100.0%)      당일 2026-07-21  vs  전영업일 2026-07-20      매수 2종목  /  매도 2종목</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="n"/>
-      <c r="C17" s="4" t="n"/>
-      <c r="D17" s="4" t="n"/>
-      <c r="E17" s="4" t="n"/>
-      <c r="F17" s="4" t="n"/>
-      <c r="G17" s="4" t="n"/>
-      <c r="H17" s="4" t="n"/>
-      <c r="I17" s="4" t="n"/>
-      <c r="J17" s="4" t="n"/>
-      <c r="K17" s="4" t="n"/>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,434억   ·   현금 45억(1.8%)      당일 2026-07-21  vs  전영업일 2026-07-20      매수 1종목  /  매도 4종목</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="4" t="n"/>
+      <c r="E13" s="4" t="n"/>
+      <c r="F13" s="4" t="n"/>
+      <c r="G13" s="4" t="n"/>
+      <c r="H13" s="4" t="n"/>
+      <c r="I13" s="4" t="n"/>
+      <c r="J13" s="4" t="n"/>
+      <c r="K13" s="4" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="n"/>
+      <c r="I14" s="8" t="n"/>
+      <c r="J14" s="8" t="n"/>
+      <c r="K14" s="8" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J15" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K15" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>지엔씨에너지  (신규)</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="n">
+        <v>350</v>
+      </c>
+      <c r="C16" s="11" t="n">
+        <v>8573250000</v>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→3.57%</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>0→350</t>
+        </is>
+      </c>
+      <c r="G16" s="14" t="inlineStr">
+        <is>
+          <t>테스</t>
+        </is>
+      </c>
+      <c r="H16" s="15" t="n">
+        <v>-40</v>
+      </c>
+      <c r="I16" s="15" t="n">
+        <v>-4714080000</v>
+      </c>
+      <c r="J16" s="16" t="inlineStr">
+        <is>
+          <t>9.62%→7.37%</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="inlineStr">
+        <is>
+          <t>190→150</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="n"/>
+      <c r="B17" s="17" t="n"/>
+      <c r="C17" s="17" t="n"/>
+      <c r="D17" s="17" t="n"/>
+      <c r="E17" s="17" t="n"/>
+      <c r="G17" s="14" t="inlineStr">
+        <is>
+          <t>브이엠</t>
+        </is>
+      </c>
+      <c r="H17" s="15" t="n">
+        <v>-20</v>
+      </c>
+      <c r="I17" s="15" t="n">
+        <v>-1283400000</v>
+      </c>
+      <c r="J17" s="16" t="inlineStr">
+        <is>
+          <t>4.23%→3.48%</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="inlineStr">
+        <is>
+          <t>150→130</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="17" t="n"/>
+      <c r="B18" s="17" t="n"/>
+      <c r="C18" s="17" t="n"/>
+      <c r="D18" s="17" t="n"/>
+      <c r="E18" s="17" t="n"/>
+      <c r="G18" s="14" t="inlineStr">
+        <is>
+          <t>주성엔지니어링</t>
+        </is>
+      </c>
+      <c r="H18" s="15" t="n">
+        <v>-20</v>
+      </c>
+      <c r="I18" s="15" t="n">
+        <v>-2317020000</v>
+      </c>
+      <c r="J18" s="16" t="inlineStr">
+        <is>
+          <t>7.35%→6.28%</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="inlineStr">
+        <is>
+          <t>150→130</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="n"/>
+      <c r="B19" s="17" t="n"/>
+      <c r="C19" s="17" t="n"/>
+      <c r="D19" s="17" t="n"/>
+      <c r="E19" s="17" t="n"/>
+      <c r="G19" s="14" t="inlineStr">
+        <is>
+          <t>피에스케이</t>
+        </is>
+      </c>
+      <c r="H19" s="15" t="n">
+        <v>-19</v>
+      </c>
+      <c r="I19" s="15" t="n">
+        <v>-2239188000</v>
+      </c>
+      <c r="J19" s="16" t="inlineStr">
+        <is>
+          <t>4.02%→2.95%</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="inlineStr">
+        <is>
+          <t>79→60</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="19" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,246억   ·   현금 26억(1.1%)      당일 2026-07-21  vs  전영업일 2026-07-20      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="4" t="n"/>
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="4" t="n"/>
+      <c r="F21" s="4" t="n"/>
+      <c r="G21" s="4" t="n"/>
+      <c r="H21" s="4" t="n"/>
+      <c r="I21" s="4" t="n"/>
+      <c r="J21" s="4" t="n"/>
+      <c r="K21" s="4" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="19" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 281억   ·   현금 2억(100.0%)      당일 2026-07-21  vs  전영업일 2026-07-20      매수 2종목  /  매도 2종목</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="4" t="n"/>
+      <c r="G24" s="4" t="n"/>
+      <c r="H24" s="4" t="n"/>
+      <c r="I24" s="4" t="n"/>
+      <c r="J24" s="4" t="n"/>
+      <c r="K24" s="4" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B18" s="6" t="n"/>
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="6" t="n"/>
-      <c r="E18" s="6" t="n"/>
-      <c r="G18" s="7" t="inlineStr">
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="G25" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H18" s="8" t="n"/>
-      <c r="I18" s="8" t="n"/>
-      <c r="J18" s="8" t="n"/>
-      <c r="K18" s="8" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="H25" s="8" t="n"/>
+      <c r="I25" s="8" t="n"/>
+      <c r="J25" s="8" t="n"/>
+      <c r="K25" s="8" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B26" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C26" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr">
+      <c r="D26" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E19" s="9" t="inlineStr">
+      <c r="E26" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G19" s="9" t="inlineStr">
+      <c r="G26" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H19" s="9" t="inlineStr">
+      <c r="H26" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I19" s="9" t="inlineStr">
+      <c r="I26" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J19" s="9" t="inlineStr">
+      <c r="J26" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K19" s="9" t="inlineStr">
+      <c r="K26" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>심텍홀딩스  (신규)</t>
         </is>
       </c>
-      <c r="B20" s="11" t="n">
+      <c r="B27" s="11" t="n">
         <v>395</v>
       </c>
-      <c r="C20" s="11" t="n">
-        <v>124059625</v>
-      </c>
-      <c r="D20" s="12" t="inlineStr">
-        <is>
-          <t>0.00%→0.37%</t>
-        </is>
-      </c>
-      <c r="E20" s="13" t="inlineStr">
+      <c r="C27" s="11" t="n">
+        <v>110402500</v>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.35%</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
         <is>
           <t>0→395</t>
         </is>
       </c>
-      <c r="G20" s="14" t="inlineStr">
+      <c r="G27" s="14" t="inlineStr">
         <is>
           <t>엘티씨</t>
         </is>
       </c>
-      <c r="H20" s="15" t="n">
+      <c r="H27" s="15" t="n">
         <v>-18</v>
       </c>
-      <c r="I20" s="15" t="n">
-        <v>-84150000</v>
-      </c>
-      <c r="J20" s="16" t="inlineStr">
-        <is>
-          <t>1.49%→1.24%</t>
-        </is>
-      </c>
-      <c r="K20" s="13" t="inlineStr">
+      <c r="I27" s="15" t="n">
+        <v>-79876800</v>
+      </c>
+      <c r="J27" s="16" t="inlineStr">
+        <is>
+          <t>1.50%→1.25%</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="inlineStr">
         <is>
           <t>107→89</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="10" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>에프앤가이드</t>
         </is>
       </c>
-      <c r="B21" s="11" t="n">
+      <c r="B28" s="11" t="n">
         <v>23</v>
       </c>
-      <c r="C21" s="11" t="n">
-        <v>41446000</v>
-      </c>
-      <c r="D21" s="12" t="inlineStr">
-        <is>
-          <t>2.96%→3.08%</t>
-        </is>
-      </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="C28" s="11" t="n">
+        <v>39164400</v>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>2.97%→3.09%</t>
+        </is>
+      </c>
+      <c r="E28" s="13" t="inlineStr">
         <is>
           <t>550→573</t>
         </is>
       </c>
-      <c r="G21" s="14" t="inlineStr">
+      <c r="G28" s="14" t="inlineStr">
         <is>
           <t>올릭스  (편출)</t>
         </is>
       </c>
-      <c r="H21" s="15" t="n">
+      <c r="H28" s="15" t="n">
         <v>-3</v>
       </c>
-      <c r="I21" s="15" t="n">
-        <v>-34833000</v>
-      </c>
-      <c r="J21" s="16" t="inlineStr">
-        <is>
-          <t>0.10%→0.00%</t>
-        </is>
-      </c>
-      <c r="K21" s="13" t="inlineStr">
+      <c r="I28" s="15" t="n">
+        <v>-29618400</v>
+      </c>
+      <c r="J28" s="16" t="inlineStr">
+        <is>
+          <t>0.09%→0.00%</t>
+        </is>
+      </c>
+      <c r="K28" s="13" t="inlineStr">
         <is>
           <t>3→0</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="19" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 528억   ·   현금 4억(0.8%)      당일 2026-07-21  vs  전영업일 2026-07-20      매수 0종목  /  매도 0종목</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="n"/>
-      <c r="C23" s="4" t="n"/>
-      <c r="D23" s="4" t="n"/>
-      <c r="E23" s="4" t="n"/>
-      <c r="F23" s="4" t="n"/>
-      <c r="G23" s="4" t="n"/>
-      <c r="H23" s="4" t="n"/>
-      <c r="I23" s="4" t="n"/>
-      <c r="J23" s="4" t="n"/>
-      <c r="K23" s="4" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="18" t="inlineStr">
-        <is>
-          <t>변화 없음 (구성종목 동일)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="19" customHeight="1">
-      <c r="A26" s="19" t="inlineStr">
+    <row r="30" ht="19" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 479억   ·   현금 0억(0.1%)      당일 2026-07-21  vs  전영업일 2026-07-20      매수 2종목  /  매도 1종목</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n"/>
+      <c r="C30" s="4" t="n"/>
+      <c r="D30" s="4" t="n"/>
+      <c r="E30" s="4" t="n"/>
+      <c r="F30" s="4" t="n"/>
+      <c r="G30" s="4" t="n"/>
+      <c r="H30" s="4" t="n"/>
+      <c r="I30" s="4" t="n"/>
+      <c r="J30" s="4" t="n"/>
+      <c r="K30" s="4" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="6" t="n"/>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H31" s="8" t="n"/>
+      <c r="I31" s="8" t="n"/>
+      <c r="J31" s="8" t="n"/>
+      <c r="K31" s="8" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G32" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H32" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I32" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J32" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K32" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>파마리서치</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="C33" s="11" t="n">
+        <v>682776000</v>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>4.77%→6.28%</t>
+        </is>
+      </c>
+      <c r="E33" s="13" t="inlineStr">
+        <is>
+          <t>64→82</t>
+        </is>
+      </c>
+      <c r="G33" s="14" t="inlineStr">
+        <is>
+          <t>코오롱티슈진</t>
+        </is>
+      </c>
+      <c r="H33" s="15" t="n">
+        <v>-59</v>
+      </c>
+      <c r="I33" s="15" t="n">
+        <v>-418852800</v>
+      </c>
+      <c r="J33" s="16" t="inlineStr">
+        <is>
+          <t>2.24%→1.49%</t>
+        </is>
+      </c>
+      <c r="K33" s="13" t="inlineStr">
+        <is>
+          <t>163→104</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>셀트리온</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C34" s="11" t="n">
+        <v>200216000</v>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>8.37%→9.09%</t>
+        </is>
+      </c>
+      <c r="E34" s="13" t="inlineStr">
+        <is>
+          <t>215→225</t>
+        </is>
+      </c>
+      <c r="G34" s="17" t="n"/>
+      <c r="H34" s="17" t="n"/>
+      <c r="I34" s="17" t="n"/>
+      <c r="J34" s="17" t="n"/>
+      <c r="K34" s="17" t="n"/>
+    </row>
+    <row r="36" ht="19" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B26" s="20" t="n"/>
-      <c r="C26" s="20" t="n"/>
-      <c r="D26" s="20" t="n"/>
-      <c r="E26" s="20" t="n"/>
-      <c r="F26" s="20" t="n"/>
-      <c r="G26" s="20" t="n"/>
-      <c r="H26" s="20" t="n"/>
-      <c r="I26" s="20" t="n"/>
-      <c r="J26" s="20" t="n"/>
-      <c r="K26" s="20" t="n"/>
+      <c r="B36" s="20" t="n"/>
+      <c r="C36" s="20" t="n"/>
+      <c r="D36" s="20" t="n"/>
+      <c r="E36" s="20" t="n"/>
+      <c r="F36" s="20" t="n"/>
+      <c r="G36" s="20" t="n"/>
+      <c r="H36" s="20" t="n"/>
+      <c r="I36" s="20" t="n"/>
+      <c r="J36" s="20" t="n"/>
+      <c r="K36" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="19">
+    <mergeCell ref="A30:K30"/>
+    <mergeCell ref="A24:K24"/>
+    <mergeCell ref="A11:K11"/>
+    <mergeCell ref="A36:K36"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A21:K21"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="G14:K14"/>
+    <mergeCell ref="A13:K13"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="G4:K4"/>
+    <mergeCell ref="A22:K22"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A23:K23"/>
-    <mergeCell ref="A26:K26"/>
-    <mergeCell ref="A15:K15"/>
-    <mergeCell ref="A24:K24"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A11:K11"/>
+    <mergeCell ref="G25:K25"/>
     <mergeCell ref="A10:K10"/>
-    <mergeCell ref="A13:K13"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A17:K17"/>
-    <mergeCell ref="G18:K18"/>
-    <mergeCell ref="G4:K4"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="G31:K31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_change_20260721.xlsx
+++ b/reports/pdf_change_20260721.xlsx
@@ -925,18 +925,18 @@
       <c r="E17" s="17" t="n"/>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-20</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-1283400000</v>
+        <v>-2317020000</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>4.23%→3.48%</t>
+          <t>7.35%→6.28%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
@@ -953,18 +953,18 @@
       <c r="E18" s="17" t="n"/>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-20</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-2317020000</v>
+        <v>-1283400000</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>7.35%→6.28%</t>
+          <t>4.23%→3.48%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">

--- a/reports/pdf_change_20260721.xlsx
+++ b/reports/pdf_change_20260721.xlsx
@@ -1124,11 +1124,11 @@
         <v>395</v>
       </c>
       <c r="C27" s="11" t="n">
-        <v>110402500</v>
+        <v>125519150</v>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.35%</t>
+          <t>0.00%→0.37%</t>
         </is>
       </c>
       <c r="E27" s="13" t="inlineStr">
@@ -1145,11 +1145,11 @@
         <v>-18</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-79876800</v>
+        <v>-85140000</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
-          <t>1.50%→1.25%</t>
+          <t>1.49%→1.24%</t>
         </is>
       </c>
       <c r="K27" s="13" t="inlineStr">
@@ -1168,11 +1168,11 @@
         <v>23</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>39164400</v>
+        <v>41933600</v>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>2.97%→3.09%</t>
+          <t>2.96%→3.08%</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
@@ -1189,11 +1189,11 @@
         <v>-3</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-29618400</v>
+        <v>-35242800</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
-          <t>0.09%→0.00%</t>
+          <t>0.10%→0.00%</t>
         </is>
       </c>
       <c r="K28" s="13" t="inlineStr">
